--- a/accor/data/eval_sim_v1_new_loo.xlsx
+++ b/accor/data/eval_sim_v1_new_loo.xlsx
@@ -10,6 +10,7 @@
     <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="predictions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="eval" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,24 +427,24 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>hotel_label</t>
+          <t>solution</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>hotel_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>hotel_brand</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>solution</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
           <t>nb_chambres</t>
@@ -466,7 +467,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>clients_jour</t>
+          <t>nb_frigos_froid</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -476,240 +477,181 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>mix_fb</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ca_reel_mensuel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ca_fb_mensuel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ca_nf_mensuel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>marge_reelle_mensuelle</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>nb_ventes_mensuel</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>nb_paniers_mensuel</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>n_mois</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>annees</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ca_ht_mensuel</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ca_fb_mensuel</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ca_nf_mensuel</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>marge_mensuel</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>nb_ventes_mensuel</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>nb_paniers_mensuel</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>mix_fb</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>mix_nf</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>taux_conversion_acheteur</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>panier_moyen_ht</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ca_par_client_heberge</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H2075</t>
+          <t>H0373</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IBB NICE</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ibis budget Nice Californie</t>
+          <t>MER MONT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>Mercure Paris Montmartre Sacré-Cœur</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
+          <t>MERCURE</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>129</v>
+        <v>305</v>
       </c>
       <c r="G2" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
-        <v>157.9</v>
-      </c>
       <c r="K2" t="n">
-        <v>4815.83</v>
+        <v>14139.8</v>
       </c>
       <c r="L2" t="n">
-        <v>30</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2023,2024,2025,2026</t>
-        </is>
+        <v>0.9594</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4125.77</v>
       </c>
       <c r="N2" t="n">
-        <v>439.71</v>
+        <v>3958.4</v>
       </c>
       <c r="O2" t="n">
-        <v>272.22</v>
+        <v>167.37</v>
       </c>
       <c r="P2" t="n">
-        <v>167.49</v>
+        <v>21.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>-165.85</v>
+        <v>564.4299999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>138.05</v>
+        <v>307.8</v>
       </c>
       <c r="S2" t="n">
-        <v>101.05</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.6191</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.3809</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.028666</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.1852</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.09130000000000001</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HB6A3</t>
+          <t>H3546</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBB STRA</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ibis budget Strasbourg Centre République</t>
+          <t>NOV TE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>Novotel Paris Centre Tour Eiffel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
+          <t>NOVOTEL</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>764</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>115.43</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3520.61</v>
+        <v>33554.88</v>
       </c>
       <c r="L3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2024,2025,2026</t>
-        </is>
+        <v>0.7413999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17839.96</v>
       </c>
       <c r="N3" t="n">
-        <v>1088.19</v>
+        <v>13225.77</v>
       </c>
       <c r="O3" t="n">
-        <v>1088.19</v>
+        <v>4614.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1396.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>-41.52</v>
+        <v>3772.78</v>
       </c>
       <c r="R3" t="n">
-        <v>347.97</v>
+        <v>1354.7</v>
       </c>
       <c r="S3" t="n">
-        <v>164.07</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.09883699999999999</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.1273</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.3091</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -720,22 +662,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>LIBERTY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>MER BOUL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Mercure Paris Boulogne</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>MERCURE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LIBERTY</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -751,51 +693,34 @@
         <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>278.86</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>8505.23</v>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2024,2025,2026</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1125.05</v>
       </c>
       <c r="N4" t="n">
         <v>1125.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1125.05</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>101.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>101.33</v>
+        <v>353.4</v>
       </c>
       <c r="R4" t="n">
-        <v>353.4</v>
+        <v>322.83</v>
       </c>
       <c r="S4" t="n">
-        <v>322.83</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.041551</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.1835</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.1323</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -806,22 +731,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>LIBERTY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>NOV MEG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Novotel Megève Mont-Blanc</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>NOVOTEL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LIBERTY</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -837,223 +762,172 @@
         <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>617.76</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>18841.68</v>
       </c>
       <c r="L5" t="n">
+        <v>0.5663</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1585.06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>897.67</v>
+      </c>
+      <c r="O5" t="n">
+        <v>687.39</v>
+      </c>
+      <c r="P5" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>223.33</v>
+      </c>
+      <c r="R5" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="S5" t="n">
         <v>26</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2024,2025,2026</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1585.06</v>
-      </c>
-      <c r="O5" t="n">
-        <v>897.67</v>
-      </c>
-      <c r="P5" t="n">
-        <v>687.39</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>123.75</v>
-      </c>
-      <c r="R5" t="n">
-        <v>223.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>128.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.5663</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.4337</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.011853</v>
-      </c>
-      <c r="W5" t="n">
-        <v>7.0973</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.08409999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H0373</t>
+          <t>H2075</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MER MONT</t>
+          <t>SIMPLY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mercure Paris Montmartre Sacré-Cœur</t>
+          <t>IBB NICE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MERCURE</t>
+          <t>Ibis budget Nice Californie</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CONNECTED</t>
+          <t>IBIS BUDGET</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>305</v>
+        <v>129</v>
       </c>
       <c r="G6" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>463.6</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>14139.8</v>
+        <v>4815.83</v>
       </c>
       <c r="L6" t="n">
-        <v>28</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2024,2025,2026</t>
-        </is>
+        <v>0.6191</v>
+      </c>
+      <c r="M6" t="n">
+        <v>439.71</v>
       </c>
       <c r="N6" t="n">
-        <v>4125.77</v>
+        <v>272.22</v>
       </c>
       <c r="O6" t="n">
-        <v>3958.4</v>
+        <v>167.49</v>
       </c>
       <c r="P6" t="n">
-        <v>167.37</v>
+        <v>-165.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.29</v>
+        <v>138.05</v>
       </c>
       <c r="R6" t="n">
-        <v>564.4299999999999</v>
+        <v>101.05</v>
       </c>
       <c r="S6" t="n">
-        <v>307.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.9594</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.0406</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.039918</v>
-      </c>
-      <c r="W6" t="n">
-        <v>7.3096</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.2918</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H3546</t>
+          <t>HB6A3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NOV TE</t>
+          <t>SIMPLY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Novotel Paris Centre Tour Eiffel</t>
+          <t>IBB STRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NOVOTEL</t>
+          <t>Ibis budget Strasbourg Centre République</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CONNECTED</t>
+          <t>IBIS BUDGET</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>764</v>
+        <v>97</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>1100.16</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>33554.88</v>
+        <v>3520.61</v>
       </c>
       <c r="L7" t="n">
-        <v>23</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2024,2025,2026</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1088.19</v>
       </c>
       <c r="N7" t="n">
-        <v>17839.96</v>
+        <v>1088.19</v>
       </c>
       <c r="O7" t="n">
-        <v>13225.77</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4614.2</v>
+        <v>-41.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1396.28</v>
+        <v>347.97</v>
       </c>
       <c r="R7" t="n">
-        <v>3772.78</v>
+        <v>164.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1354.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.7413999999999999</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.2586</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.112436</v>
-      </c>
-      <c r="W7" t="n">
-        <v>4.7286</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.5317</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,119 +957,163 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>peers</t>
+          <t>ca_reel</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ca_reel</t>
+          <t>ca_pred</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ca_pred</t>
+          <t>ca_err_abs</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ca_err_abs</t>
+          <t>marge_reel</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>marge_reel</t>
+          <t>marge_pred</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>marge_pred</t>
+          <t>marge_err_abs</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>marge_err_abs</t>
+          <t>n_mois</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>n_mois</t>
+          <t>clients_hotel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>taux_acheteurs</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mix_steps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>r4_mode</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>r4_diff</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H2075</t>
+          <t>H0373</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
+          <t>CONNECTED</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4125.77</v>
       </c>
       <c r="D2" t="n">
-        <v>439.71</v>
+        <v>13763.77397182734</v>
       </c>
       <c r="E2" t="n">
-        <v>2291.58</v>
+        <v>9638.00397182734</v>
       </c>
       <c r="F2" t="n">
-        <v>1851.87</v>
+        <v>21.29</v>
       </c>
       <c r="G2" t="n">
-        <v>-165.85</v>
+        <v>8089.263722709286</v>
       </c>
       <c r="H2" t="n">
-        <v>1362.03</v>
+        <v>8067.973722709286</v>
       </c>
       <c r="I2" t="n">
-        <v>1527.88</v>
+        <v>28</v>
       </c>
       <c r="J2" t="n">
-        <v>30</v>
+        <v>14139.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1124361046738954</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.180000000000001</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>frigos_froid</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HB6A3</t>
+          <t>H3546</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>H2075</t>
-        </is>
+          <t>CONNECTED</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17839.96</v>
       </c>
       <c r="D3" t="n">
-        <v>1088.19</v>
+        <v>13202.17095293028</v>
       </c>
       <c r="E3" t="n">
-        <v>379.42</v>
+        <v>4637.789047069718</v>
       </c>
       <c r="F3" t="n">
-        <v>708.77</v>
+        <v>1396.28</v>
       </c>
       <c r="G3" t="n">
-        <v>-41.52</v>
+        <v>7948.472074879434</v>
       </c>
       <c r="H3" t="n">
-        <v>226.73</v>
+        <v>6552.192074879435</v>
       </c>
       <c r="I3" t="n">
-        <v>268.25</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>33554.88</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.03991782061981074</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2.180000000000001</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>frigos_froid</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1209,31 +1127,43 @@
           <t>LIBERTY</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HB5I0</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1125.05</v>
       </c>
       <c r="D4" t="n">
-        <v>1125.05</v>
+        <v>795.8292544112999</v>
       </c>
       <c r="E4" t="n">
-        <v>795.83</v>
+        <v>329.2207455887001</v>
       </c>
       <c r="F4" t="n">
-        <v>329.22</v>
+        <v>101.33</v>
       </c>
       <c r="G4" t="n">
-        <v>101.33</v>
+        <v>537.2238814061591</v>
       </c>
       <c r="H4" t="n">
-        <v>537.22</v>
+        <v>435.8938814061591</v>
       </c>
       <c r="I4" t="n">
-        <v>435.89</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>21</v>
+        <v>8505.23</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01185297701691144</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.337</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>m_lin</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="5">
@@ -1247,107 +1177,143 @@
           <t>LIBERTY</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>H6188</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1585.06</v>
       </c>
       <c r="D5" t="n">
-        <v>1585.06</v>
+        <v>4156.761461920194</v>
       </c>
       <c r="E5" t="n">
-        <v>4156.76</v>
+        <v>2571.701461920194</v>
       </c>
       <c r="F5" t="n">
-        <v>2571.7</v>
+        <v>123.75</v>
       </c>
       <c r="G5" t="n">
-        <v>123.75</v>
+        <v>2309.326311137449</v>
       </c>
       <c r="H5" t="n">
-        <v>2309.33</v>
+        <v>2185.576311137449</v>
       </c>
       <c r="I5" t="n">
-        <v>2185.58</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>26</v>
+        <v>18841.68</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.04155090456107595</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-4.337</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>m_lin</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H0373</t>
+          <t>H2075</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONNECTED</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>H3546</t>
-        </is>
+          <t>SIMPLY</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>439.71</v>
       </c>
       <c r="D6" t="n">
-        <v>4125.77</v>
+        <v>2291.580028164406</v>
       </c>
       <c r="E6" t="n">
-        <v>13763.77</v>
+        <v>1851.870028164406</v>
       </c>
       <c r="F6" t="n">
-        <v>9638</v>
+        <v>-165.85</v>
       </c>
       <c r="G6" t="n">
-        <v>21.29</v>
+        <v>1362.035394617088</v>
       </c>
       <c r="H6" t="n">
-        <v>8089.26</v>
+        <v>1527.885394617088</v>
       </c>
       <c r="I6" t="n">
-        <v>8067.97</v>
+        <v>30</v>
       </c>
       <c r="J6" t="n">
-        <v>28</v>
+        <v>4815.83</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.09883798546274651</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-3.809</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>m_lin</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H3546</t>
+          <t>HB6A3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CONNECTED</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>H0373</t>
-        </is>
+          <t>SIMPLY</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1088.19</v>
       </c>
       <c r="D7" t="n">
-        <v>17839.96</v>
+        <v>379.4183245949843</v>
       </c>
       <c r="E7" t="n">
-        <v>13202.17</v>
+        <v>708.7716754050157</v>
       </c>
       <c r="F7" t="n">
-        <v>4637.79</v>
+        <v>-41.52</v>
       </c>
       <c r="G7" t="n">
-        <v>1396.28</v>
+        <v>226.7255004103966</v>
       </c>
       <c r="H7" t="n">
-        <v>7948.47</v>
+        <v>268.2455004103966</v>
       </c>
       <c r="I7" t="n">
-        <v>6552.19</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>3520.61</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02866587898659214</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.809</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>m_lin</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -1361,13 +1327,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>perimetre</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1388,45 +1354,56 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>mape_ca_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mape_marge_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3289.56</v>
+        <v>3289.559488329229</v>
       </c>
       <c r="D2" t="n">
-        <v>3172.96</v>
+        <v>3172.961147526636</v>
       </c>
       <c r="E2" t="n">
-        <v>156.2</v>
+        <v>156.2334840672533</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7021.411069991372</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1280.32</v>
+        <v>7137.896509448529</v>
       </c>
       <c r="D3" t="n">
-        <v>898.0700000000001</v>
+        <v>7310.082898794361</v>
       </c>
       <c r="E3" t="n">
-        <v>243.1</v>
+        <v>129.8008042687997</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19182.43143971156</v>
       </c>
     </row>
     <row r="4">
@@ -1439,33 +1416,471 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1450.46</v>
+        <v>1450.461103754447</v>
       </c>
       <c r="D4" t="n">
-        <v>1310.73</v>
+        <v>1310.735096271804</v>
       </c>
       <c r="E4" t="n">
-        <v>95.8</v>
+        <v>95.75454102805327</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1098.147428819209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONNECTED</t>
+          <t>SIMPLY</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7137.9</v>
+        <v>1280.320851784711</v>
       </c>
       <c r="D5" t="n">
-        <v>7310.08</v>
+        <v>898.0654475137424</v>
       </c>
       <c r="E5" t="n">
-        <v>129.8</v>
-      </c>
+        <v>243.1451069049069</v>
+      </c>
+      <c r="F5" t="n">
+        <v>783.6543414433454</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>hotel_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>solution</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ca_ht_reel</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ca_ht_pred</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>erreur_abs_ca</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>marge_reel</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>marge_pred</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>erreur_abs_marge</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>n_mois</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>clients_hotel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>taux_acheteurs</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mix_steps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>r4_mode</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>r4_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H0373</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CONNECTED</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4125.77</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13763.77397182734</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9638.00397182734</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8089.263722709286</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8067.973722709286</v>
+      </c>
+      <c r="I2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14139.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1124361046738954</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.180000000000001</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>frigos_froid</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H3546</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CONNECTED</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17839.96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13202.17095293028</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4637.789047069718</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1396.28</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7948.472074879434</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6552.192074879435</v>
+      </c>
+      <c r="I3" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33554.88</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.03991782061981074</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2.180000000000001</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>frigos_froid</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H6188</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIBERTY</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1125.05</v>
+      </c>
+      <c r="D4" t="n">
+        <v>795.8292544112999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>329.2207455887001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="G4" t="n">
+        <v>537.2238814061591</v>
+      </c>
+      <c r="H4" t="n">
+        <v>435.8938814061591</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8505.23</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01185297701691144</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.337</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>m_lin</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HB5I0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIBERTY</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1585.06</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4156.761461920194</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2571.701461920194</v>
+      </c>
+      <c r="F5" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2309.326311137449</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2185.576311137449</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18841.68</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.04155090456107595</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-4.337</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>m_lin</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>H2075</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SIMPLY</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>439.71</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2291.580028164406</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1851.870028164406</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-165.85</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1362.035394617088</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1527.885394617088</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4815.83</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.09883798546274651</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-3.809</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>m_lin</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HB6A3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SIMPLY</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1088.19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>379.4183245949843</v>
+      </c>
+      <c r="E7" t="n">
+        <v>708.7716754050157</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-41.52</v>
+      </c>
+      <c r="G7" t="n">
+        <v>226.7255004103966</v>
+      </c>
+      <c r="H7" t="n">
+        <v>268.2455004103966</v>
+      </c>
+      <c r="I7" t="n">
+        <v>19</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3520.61</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02866587898659214</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.809</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>m_lin</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MAE_GLOBAL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3289.559488329229</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>3172.961147526636</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MAPE_CA_PCT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>156.2334840672533</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
